--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/nuble.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/nuble.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M72"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>15084.06</v>
+        <v>15001.61</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>8433.52</v>
+        <v>8387.43</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>3715.3</v>
+        <v>3728.56</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2112.6</v>
+        <v>2135.57</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>27125</v>
+        <v>27593.22</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>12942.13</v>
+        <v>13165.53</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>752.48</v>
+        <v>757.9</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>5182.53</v>
+        <v>5173.33</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>15398.67</v>
+        <v>15374.8</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2835.19</v>
+        <v>2849.84</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>3140.01</v>
+        <v>3162.17</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>2877.31</v>
+        <v>2848.69</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1198.3</v>
+        <v>1186.37</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>27899.31</v>
+        <v>27621.72</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>42297.97</v>
+        <v>41877.12</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1153.74</v>
+        <v>1140.39</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>41750.21</v>
+        <v>41267.03</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>4866.38</v>
+        <v>4825.15</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>70512.69</v>
+        <v>70783.33</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1032.88</v>
+        <v>1036.85</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>908.1900000000001</v>
+        <v>912.3</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1041.24</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>67867.28999999999</v>
+        <v>68047.25999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>10951.29</v>
+        <v>10980.33</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>893.59</v>
+        <v>892.33</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>10545.98</v>
+        <v>10531.18</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>52024.57</v>
+        <v>52091.27</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>926.14</v>
+        <v>914.38</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>15472.38</v>
+        <v>15390.65</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1920.09</v>
+        <v>1909.95</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>65413.61</v>
+        <v>67004.32000000001</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>3626.21</v>
+        <v>3733.99</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1140.85</v>
+        <v>1151.01</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>948.71</v>
+        <v>936.5</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>3004.64</v>
+        <v>3051.71</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>3929.27</v>
+        <v>3945.5</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2301.76</v>
+        <v>2275.18</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1344.24</v>
+        <v>1336.52</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1892.38</v>
+        <v>1848.34</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>784.4</v>
+        <v>759.39</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>918.15</v>
+        <v>929.45</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>2526.35</v>
+        <v>2559.99</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>2045.44</v>
+        <v>2072.13</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>3505.25</v>
+        <v>3550.99</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>2486.49</v>
+        <v>2495.91</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>1108.32</v>
+        <v>1105.53</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>870.2</v>
+        <v>874.47</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>8832.950000000001</v>
+        <v>8879.92</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>3148.79</v>
+        <v>3165.53</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>2919.74</v>
+        <v>2961.51</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>1229.91</v>
+        <v>1250.71</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>2293.23</v>
+        <v>2316.55</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1180.96</v>
+        <v>1192.97</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>985.46</v>
+        <v>971.48</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>3984.9</v>
+        <v>4002.99</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>3821.64</v>
+        <v>3894.3</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>4116.72</v>
+        <v>4194.99</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>2722.27</v>
+        <v>2774.02</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>9662.85</v>
+        <v>9846.559999999999</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>3810.05</v>
+        <v>3759.3</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>3407.16</v>
+        <v>3439.53</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>3832.44</v>
+        <v>3870.98</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>3927.2</v>
+        <v>3907.3</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>7076.31</v>
+        <v>7040.47</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>2135.3</v>
+        <v>2139.85</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>4039.45</v>
+        <v>4048.06</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>16099.1</v>
+        <v>16204.05</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>1718.4</v>
+        <v>1729.9</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>1125.97</v>
+        <v>1122.41</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>46984.66</v>
+        <v>46890.47</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,68 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>42964.07</v>
+        <v>43251.65</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>5040-135-CM26</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>69.141.400-0</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>FERNANDO ALBERTO VELOSO OLIVA</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>14.205.876-6</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>20916.56</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/nuble.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/nuble.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M172"/>
+  <dimension ref="A1:M180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3564,7 +3564,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1233616-7269-CM25</t>
+          <t>1233616-7267-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>1049.06</v>
+        <v>1573.58</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1233616-7270-CM25</t>
+          <t>1233616-7269-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3686,7 +3686,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1233616-7272-CM25</t>
+          <t>1233616-7270-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3747,7 +3747,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1233616-7273-CM25</t>
+          <t>1233616-7272-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>786.79</v>
+        <v>1049.06</v>
       </c>
     </row>
     <row r="56">
@@ -3869,7 +3869,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1233616-7267-CM25</t>
+          <t>1233616-7273-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>1573.58</v>
+        <v>786.79</v>
       </c>
     </row>
     <row r="58">
@@ -3991,7 +3991,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1346280-11-CM25</t>
+          <t>1233616-7323-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4016,12 +4016,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.141.400-0</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>FERNANDO ALBERTO VELOSO OLIVA</t>
+          <t>KINSA SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>14.205.876-6</t>
+          <t>77.049.323-4</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>3184.57</v>
+        <v>788.37</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1233616-7323-CM25</t>
+          <t>1346280-11-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>69.141.400-0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>KINSA SPA</t>
+          <t>FERNANDO ALBERTO VELOSO OLIVA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>77.049.323-4</t>
+          <t>14.205.876-6</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>788.37</v>
+        <v>3184.57</v>
       </c>
     </row>
     <row r="61">
@@ -4784,7 +4784,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1233616-7454-CM25</t>
+          <t>1079580-274-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>62.000.520-7</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>KINSA SPA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>77.049.323-4</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>1539.53</v>
+        <v>19968.34</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1079580-274-CM25</t>
+          <t>1233616-7454-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>62.000.520-7</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>KINSA SPA</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>77.049.323-4</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>19968.34</v>
+        <v>1539.53</v>
       </c>
     </row>
     <row r="74">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XVI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XVI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6858,7 +6858,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1155683-339-CM25</t>
+          <t>1233616-18372-CM25</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>96.792.430-K</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -6913,13 +6913,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>27621.72</v>
+        <v>1186.37</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1233616-18372-CM25</t>
+          <t>1233616-18368-CM25</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -6974,13 +6974,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>1186.37</v>
+        <v>2848.69</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1233616-18368-CM25</t>
+          <t>1155683-339-CM25</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7020,12 +7020,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>2848.69</v>
+        <v>27621.72</v>
       </c>
     </row>
     <row r="109">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -7102,7 +7102,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>3588-582-CM25</t>
+          <t>2467-4755-CM25</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7127,12 +7127,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>69.141.500-7</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE YUNGAY</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7142,12 +7142,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>BROKER SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>77.819.582-8</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -7157,13 +7157,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>41267.03</v>
+        <v>1140.39</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2467-4755-CM25</t>
+          <t>3588-582-CM25</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.141.500-7</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>I MUNICIPALIDAD DE YUNGAY</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7203,12 +7203,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>BROKER SPA</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>77.819.582-8</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>1140.39</v>
+        <v>41267.03</v>
       </c>
     </row>
     <row r="112">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Dirección de Vialidad - Región XVI - Punilla</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8047,7 +8047,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XVI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8139,7 +8139,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2467-68-CM26</t>
+          <t>1059082-3-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8154,22 +8154,22 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K127" t="inlineStr"/>
@@ -8194,13 +8194,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>1151.01</v>
+        <v>1450.56</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1011183-4-CM26</t>
+          <t>2467-68-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -8225,12 +8225,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8240,12 +8240,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K128" t="inlineStr"/>
@@ -8255,13 +8255,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>936.5</v>
+        <v>1151.01</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2467-162-CM26</t>
+          <t>1011183-4-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>FERNANDO ALBERTO VELOSO OLIVA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>14.205.876-6</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K129" t="inlineStr"/>
@@ -8316,13 +8316,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>3051.71</v>
+        <v>936.5</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1079580-52-CM26</t>
+          <t>2467-162-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8337,22 +8337,22 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>62.000.520-7</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XVI ZONA</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8362,12 +8362,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>FRANCISCO JAVIER</t>
+          <t>FERNANDO ALBERTO VELOSO OLIVA</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>76.882.403-7</t>
+          <t>14.205.876-6</t>
         </is>
       </c>
       <c r="K130" t="inlineStr"/>
@@ -8377,13 +8377,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>3945.5</v>
+        <v>3051.71</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>3659-206-CM26</t>
+          <t>1079580-52-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8398,22 +8398,22 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>62.000.520-7</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>Francisco javier</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.882.403-7</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
@@ -8438,13 +8438,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>2275.18</v>
+        <v>3945.5</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>3482-37-CM26</t>
+          <t>3659-206-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8459,22 +8459,22 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>61.962.200-6</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>FRANCISCO JAVIER</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>76.882.403-7</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -8499,13 +8499,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>1336.52</v>
+        <v>2275.18</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2467-219-CM26</t>
+          <t>3482-37-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8520,22 +8520,22 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>61.962.200-6</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>Francisco javier</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>76.882.403-7</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
@@ -8560,13 +8560,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>1848.34</v>
+        <v>1336.52</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1051765-244-CM26</t>
+          <t>2467-219-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8576,27 +8576,27 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>62.000.570-3</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -8621,13 +8621,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>759.39</v>
+        <v>1848.34</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1072229-58-CM26</t>
+          <t>1051765-244-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8642,22 +8642,22 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>62.000.570-3</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>SOSEG SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>76.897.534-5</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K135" t="inlineStr"/>
@@ -8682,13 +8682,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>929.45</v>
+        <v>759.39</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>3659-288-CM26</t>
+          <t>1072229-58-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8703,7 +8703,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8728,12 +8728,12 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>COMERCIAL COMPARO LIMITADA</t>
+          <t>SOSEG SPA</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>76.290.943-K</t>
+          <t>76.897.534-5</t>
         </is>
       </c>
       <c r="K136" t="inlineStr"/>
@@ -8743,13 +8743,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>2559.99</v>
+        <v>929.45</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1346280-3-CM26</t>
+          <t>3659-288-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8764,22 +8764,22 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>69.141.400-0</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE QUILLÓN</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8789,12 +8789,12 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL COMPARO LIMITADA</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>76.290.943-K</t>
         </is>
       </c>
       <c r="K137" t="inlineStr"/>
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>2072.13</v>
+        <v>2559.99</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1346280-4-CM26</t>
+          <t>1346280-3-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE QUILLÓN</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8850,12 +8850,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K138" t="inlineStr"/>
@@ -8865,13 +8865,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>3550.99</v>
+        <v>2072.13</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>4594-404-CM26</t>
+          <t>1346280-4-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8881,27 +8881,27 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>69.141.102-8</t>
+          <t>69.141.400-0</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8911,12 +8911,12 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K139" t="inlineStr"/>
@@ -8926,13 +8926,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>2495.91</v>
+        <v>3550.99</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1067526-75-CM26</t>
+          <t>4594-404-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8947,22 +8947,22 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>69.141.102-8</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>MAR DEL SUR SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>83.610.800-0</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K140" t="inlineStr"/>
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>1105.53</v>
+        <v>2495.91</v>
       </c>
     </row>
     <row r="141">
@@ -9135,7 +9135,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -9298,7 +9298,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2467-595-CM26</t>
+          <t>2467-593-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9338,12 +9338,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>BIKE RED MACHINE SPA</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.856.309-8</t>
         </is>
       </c>
       <c r="K146" t="inlineStr"/>
@@ -9353,13 +9353,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>1192.97</v>
+        <v>2316.55</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2467-593-CM26</t>
+          <t>2467-595-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9399,12 +9399,12 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>BIKE RED MACHINE SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>76.856.309-8</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K147" t="inlineStr"/>
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>2316.55</v>
+        <v>1192.97</v>
       </c>
     </row>
     <row r="148">
@@ -9542,7 +9542,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2467-673-CM26</t>
+          <t>2467-676-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9582,12 +9582,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
@@ -9597,13 +9597,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>3894.3</v>
+        <v>9846.559999999999</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2467-674-CM26</t>
+          <t>2467-675-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9643,12 +9643,12 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>IMPORTADORA Y COMERCIALIZADORA DE SISTEMAS GENERADORES DE ENERGIA POWE</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>76.206.192-9</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
@@ -9658,13 +9658,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>4194.99</v>
+        <v>2774.02</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2467-675-CM26</t>
+          <t>2467-673-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA DE SISTEMAS GENERADORES DE ENERGIA POWE</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>76.206.192-9</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K152" t="inlineStr"/>
@@ -9719,13 +9719,13 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>2774.02</v>
+        <v>3894.3</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2467-676-CM26</t>
+          <t>2467-674-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>9846.559999999999</v>
+        <v>4194.99</v>
       </c>
     </row>
     <row r="154">
@@ -9969,7 +9969,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2467-805-CM26</t>
+          <t>2467-802-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10009,12 +10009,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K157" t="inlineStr"/>
@@ -10024,13 +10024,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>3907.3</v>
+        <v>7040.47</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2467-802-CM26</t>
+          <t>2467-805-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10070,12 +10070,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>7040.47</v>
+        <v>3907.3</v>
       </c>
     </row>
     <row r="159">
@@ -10274,7 +10274,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2467-795-CM26</t>
+          <t>1375761-1287-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>61.981.330-8</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10314,12 +10314,12 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K162" t="inlineStr"/>
@@ -10329,13 +10329,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>1729.9</v>
+        <v>7687.34</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1072229-124-CM26</t>
+          <t>2467-795-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10350,7 +10350,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K163" t="inlineStr"/>
@@ -10390,13 +10390,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>1122.41</v>
+        <v>1729.9</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1171317-38-CM26</t>
+          <t>1375761-1284-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -10421,12 +10421,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>61.981.330-8</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K164" t="inlineStr"/>
@@ -10451,13 +10451,13 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>46890.47</v>
+        <v>16230.09</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1233616-1387-CM26</t>
+          <t>1072229-124-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10472,7 +10472,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -10482,12 +10482,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10497,12 +10497,12 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>BROKER SPA</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>77.819.582-8</t>
+          <t>96.792.430-K</t>
         </is>
       </c>
       <c r="K165" t="inlineStr"/>
@@ -10512,13 +10512,13 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>43251.65</v>
+        <v>1122.41</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2467-901-CM26</t>
+          <t>1171317-38-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10528,12 +10528,12 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -10558,12 +10558,12 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>FERNANDO ALBERTO VELOSO OLIVA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>14.205.876-6</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K166" t="inlineStr"/>
@@ -10573,13 +10573,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>3510.99</v>
+        <v>46890.47</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>3659-669-CM26</t>
+          <t>1375761-1335-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10589,27 +10589,27 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>61.981.330-8</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10619,12 +10619,12 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>COMERCIAL RENHET SPA</t>
+          <t>COMERCIAL COMPARO LIMITADA</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>77.619.564-2</t>
+          <t>76.290.943-K</t>
         </is>
       </c>
       <c r="K167" t="inlineStr"/>
@@ -10634,13 +10634,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>898.79</v>
+        <v>65542.09</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>5040-135-CM26</t>
+          <t>1233616-1387-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10650,27 +10650,27 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>69.141.400-0</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>FERNANDO ALBERTO VELOSO OLIVA</t>
+          <t>BROKER SPA</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>14.205.876-6</t>
+          <t>77.819.582-8</t>
         </is>
       </c>
       <c r="K168" t="inlineStr"/>
@@ -10695,13 +10695,13 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>20916.56</v>
+        <v>43251.65</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1079580-324-CM26</t>
+          <t>2467-901-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10716,7 +10716,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -10726,12 +10726,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>62.000.520-7</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10741,12 +10741,12 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>FERNANDO ALBERTO VELOSO OLIVA</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>14.205.876-6</t>
         </is>
       </c>
       <c r="K169" t="inlineStr"/>
@@ -10756,13 +10756,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>28309.1</v>
+        <v>3510.99</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1079580-330-CM26</t>
+          <t>3659-669-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10777,7 +10777,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>62.000.520-7</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -10802,12 +10802,12 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>COMERCIAL RENHET SPA</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>77.619.564-2</t>
         </is>
       </c>
       <c r="K170" t="inlineStr"/>
@@ -10817,13 +10817,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>1193.6</v>
+        <v>898.79</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1375761-1533-CM26</t>
+          <t>5040-135-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10838,22 +10838,22 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>61.981.330-8</t>
+          <t>69.141.400-0</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -10863,12 +10863,12 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>FERNANDO ALBERTO VELOSO OLIVA</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>14.205.876-6</t>
         </is>
       </c>
       <c r="K171" t="inlineStr"/>
@@ -10878,13 +10878,13 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>7929.25</v>
+        <v>20916.56</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>4174-421-CM26</t>
+          <t>1079580-324-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10899,7 +10899,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>69.140.100-6</t>
+          <t>62.000.520-7</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Quirihue</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -10924,12 +10924,12 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K172" t="inlineStr"/>
@@ -10939,7 +10939,495 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
+        <v>28309.1</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>1375761-1533-CM26</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>61.981.330-8</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="n">
+        <v>7929.25</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>1079580-330-CM26</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>62.000.520-7</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>GIOVANNI SEBASTIAN</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>76.737.293-0</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="n">
+        <v>1193.6</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>4174-421-CM26</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>69.140.100-6</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Quirihue</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>76.961.103-7</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="n">
         <v>6838.86</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2467-1104-CM26</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>69.140.900-7</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M176" s="2" t="n">
+        <v>8224.08</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2467-1186-CM26</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>69.140.900-7</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="n">
+        <v>5236.9</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2724-862-CM26</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>69.140.500-1</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M178" s="2" t="n">
+        <v>36540.23</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>1534596-15-CM26</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>62.000.520-7</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>COMERCIAL GRAN VIA SPA</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M179" s="2" t="n">
+        <v>2692.76</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>1375761-1800-CM26</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>61.981.330-8</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>COMERCIAL TRANCURA SPA</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>77.823.479-3</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M180" s="2" t="n">
+        <v>11504.32</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/nuble.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/nuble.xlsx
@@ -684,7 +684,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +749,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +936,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1001,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1188,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1802,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2843,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +2969,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3034,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3465,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3530,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5303,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5612,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +5921,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6230,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6356,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7031,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7096,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7283,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7470,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7535,11 @@
           <t>77.798.686-4</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +7783,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +7848,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +7974,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +8588,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +8775,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9023,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9088,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9153,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9218,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9405,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9470,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9535,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +9600,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +9726,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +9852,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +9917,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +9982,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10169,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10234,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10299,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10364,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10429,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10494,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +10559,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +10624,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10688,7 +10872,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +10998,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11185,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11372,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11237,7 +11437,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +11502,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +11567,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +11632,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/nuble.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/nuble.xlsx
@@ -1680,7 +1680,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4815,7 +4819,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5059,7 +5067,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5242,7 +5254,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7161,7 +7177,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8962,7 +8982,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/nuble.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/nuble.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M180"/>
+  <dimension ref="A1:M187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1266,7 +1266,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4366-10-CM25</t>
+          <t>1030177-30-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1327,7 +1327,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1030177-30-CM25</t>
+          <t>4366-10-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1823,7 +1823,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1233616-6394-CM25</t>
+          <t>1233616-6396-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1878,13 +1878,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>2455.66</v>
+        <v>982.26</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1233616-6395-CM25</t>
+          <t>1233616-6394-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>2946.79</v>
+        <v>2455.66</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1233616-6396-CM25</t>
+          <t>1233616-6395-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>982.26</v>
+        <v>2946.79</v>
       </c>
     </row>
     <row r="26">
@@ -2189,7 +2189,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>4594-320-CM25</t>
+          <t>3673-160-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.141.102-8</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COIHUECO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>CROBAK SPA</t>
+          <t>SOSEG SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>77.071.404-4</t>
+          <t>76.897.534-5</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2244,13 +2244,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>6243.82</v>
+        <v>4417.53</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3673-160-CM25</t>
+          <t>4594-320-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2275,12 +2275,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>69.141.102-8</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2290,12 +2290,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>SOSEG SPA</t>
+          <t>CROBAK SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.897.534-5</t>
+          <t>77.071.404-4</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>4417.53</v>
+        <v>6243.82</v>
       </c>
     </row>
     <row r="31">
@@ -3551,7 +3551,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1233616-7265-CM25</t>
+          <t>1233616-7267-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3612,7 +3612,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1233616-7267-CM25</t>
+          <t>1233616-7269-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3667,13 +3667,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>1573.58</v>
+        <v>1049.06</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1233616-7269-CM25</t>
+          <t>1233616-7270-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3734,7 +3734,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1233616-7270-CM25</t>
+          <t>1233616-7272-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3795,7 +3795,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1233616-7272-CM25</t>
+          <t>1233616-7273-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>1049.06</v>
+        <v>786.79</v>
       </c>
     </row>
     <row r="56">
@@ -3917,7 +3917,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1233616-7273-CM25</t>
+          <t>1233616-7265-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>786.79</v>
+        <v>1573.58</v>
       </c>
     </row>
     <row r="58">
@@ -4039,7 +4039,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1233616-7323-CM25</t>
+          <t>1346280-11-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>69.141.400-0</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>KINSA SPA</t>
+          <t>FERNANDO ALBERTO VELOSO OLIVA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>77.049.323-4</t>
+          <t>14.205.876-6</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4094,13 +4094,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>788.37</v>
+        <v>3184.57</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1346280-11-CM25</t>
+          <t>1233616-7323-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>69.141.400-0</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>FERNANDO ALBERTO VELOSO OLIVA</t>
+          <t>KINSA SPA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>14.205.876-6</t>
+          <t>77.049.323-4</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4155,7 +4155,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>3184.57</v>
+        <v>788.37</v>
       </c>
     </row>
     <row r="61">
@@ -4836,7 +4836,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1079580-274-CM25</t>
+          <t>1233616-7454-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>62.000.520-7</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>KINSA SPA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>77.049.323-4</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4891,13 +4891,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>19968.34</v>
+        <v>1539.53</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1233616-7454-CM25</t>
+          <t>1079580-274-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>62.000.520-7</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>KINSA SPA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>77.049.323-4</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>1539.53</v>
+        <v>19968.34</v>
       </c>
     </row>
     <row r="74">
@@ -5767,7 +5767,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>229-926-CM25</t>
+          <t>2467-1773-CM25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>69.141.100-1</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COIHUECO</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>FERNANDO ALBERTO VELOSO OLIVA</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>14.205.876-6</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>1463.51</v>
+        <v>1919.51</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2467-1773-CM25</t>
+          <t>229-926-CM25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.141.100-1</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>FERNANDO ALBERTO VELOSO OLIVA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>14.205.876-6</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5883,13 +5883,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>1919.51</v>
+        <v>1463.51</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1079580-420-CM25</t>
+          <t>229-923-CM25</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5909,17 +5909,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>62.000.520-7</t>
+          <t>69.141.100-1</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5929,32 +5929,28 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>96.792.430-K</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>6113.77</v>
+        <v>1661.43</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>229-923-CM25</t>
+          <t>1079580-420-CM25</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5974,17 +5970,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>69.141.100-1</t>
+          <t>62.000.520-7</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COIHUECO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5994,22 +5990,26 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>1661.43</v>
+        <v>6113.77</v>
       </c>
     </row>
     <row r="91">
@@ -6263,7 +6263,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1171317-52-CM25</t>
+          <t>1079580-475-CM25</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6283,17 +6283,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>62.000.520-7</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6303,28 +6303,32 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>15001.61</v>
+        <v>8387.43</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1079580-475-CM25</t>
+          <t>1171317-52-CM25</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6344,17 +6348,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>62.000.520-7</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6364,26 +6368,22 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.962.756-1</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>8387.43</v>
+        <v>15001.61</v>
       </c>
     </row>
     <row r="97">
@@ -6938,7 +6938,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1233616-18372-CM25</t>
+          <t>1233616-18374-CM25</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6978,28 +6978,32 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr"/>
+          <t>76.287.853-4</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>1186.37</v>
+        <v>41877.12</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1233616-18368-CM25</t>
+          <t>1155683-339-CM25</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7024,12 +7028,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7039,17 +7043,17 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -7058,13 +7062,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>2848.69</v>
+        <v>27621.72</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1155683-339-CM25</t>
+          <t>1233616-18372-CM25</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7089,12 +7093,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7104,32 +7108,28 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>96.792.430-K</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>27621.72</v>
+        <v>1186.37</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1233616-18374-CM25</t>
+          <t>1233616-18368-CM25</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7169,12 +7169,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -7188,7 +7188,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>41877.12</v>
+        <v>2848.69</v>
       </c>
     </row>
     <row r="110">
@@ -8011,7 +8011,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1233616-167-CM26</t>
+          <t>1233616-168-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8066,13 +8066,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>15390.65</v>
+        <v>1909.95</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1233616-168-CM26</t>
+          <t>1233616-167-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8127,7 +8127,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>1909.95</v>
+        <v>15390.65</v>
       </c>
     </row>
     <row r="125">
@@ -9702,7 +9702,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2467-676-CM26</t>
+          <t>2467-675-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9742,32 +9742,28 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>IMPORTADORA Y COMERCIALIZADORA DE SISTEMAS GENERADORES DE ENERGIA POWE</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>76.206.192-9</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>9846.559999999999</v>
+        <v>2774.02</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2467-675-CM26</t>
+          <t>2467-676-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9807,28 +9803,32 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA DE SISTEMAS GENERADORES DE ENERGIA POWE</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>76.206.192-9</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>2774.02</v>
+        <v>9846.559999999999</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2467-673-CM26</t>
+          <t>2467-674-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -9887,13 +9887,13 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>3894.3</v>
+        <v>4194.99</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2467-674-CM26</t>
+          <t>2467-673-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -9952,7 +9952,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>4194.99</v>
+        <v>3894.3</v>
       </c>
     </row>
     <row r="154">
@@ -10470,7 +10470,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1375761-1287-CM26</t>
+          <t>2467-795-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10495,12 +10495,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>61.981.330-8</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10510,17 +10510,17 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -10529,13 +10529,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>7687.34</v>
+        <v>1729.9</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2467-795-CM26</t>
+          <t>1375761-1287-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10560,12 +10560,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>61.981.330-8</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10575,17 +10575,17 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -10594,7 +10594,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>1729.9</v>
+        <v>7687.34</v>
       </c>
     </row>
     <row r="164">
@@ -11161,7 +11161,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1375761-1533-CM26</t>
+          <t>1079580-330-CM26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11181,17 +11181,17 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>61.981.330-8</t>
+          <t>62.000.520-7</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11201,32 +11201,28 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>76.737.293-0</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>7929.25</v>
+        <v>1193.6</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1079580-330-CM26</t>
+          <t>1375761-1533-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11246,17 +11242,17 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>62.000.520-7</t>
+          <t>61.981.330-8</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11266,22 +11262,26 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
-        </is>
-      </c>
-      <c r="K174" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>1193.6</v>
+        <v>7929.25</v>
       </c>
     </row>
     <row r="175">
@@ -11498,7 +11498,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -11628,7 +11628,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -11668,6 +11668,445 @@
       </c>
       <c r="M180" s="2" t="n">
         <v>11504.32</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>1059082-60-CM26</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M181" s="2" t="n">
+        <v>748.3200000000001</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>1233616-1844-CM26</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>61.980.940-8</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>COMERCIAL RENHET SPA</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>77.619.564-2</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M182" s="2" t="n">
+        <v>1211.34</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>1030177-135-CM26</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>69.141.400-0</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Francisco javier</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>76.882.403-7</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M183" s="2" t="n">
+        <v>3008.92</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>1495208-34-CM26</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>61.981.340-5</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>QUIMICA PASSOL S.A.</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>84.634.200-1</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M184" s="2" t="n">
+        <v>785.37</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>1495208-33-CM26</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>61.981.340-5</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Comercial IBL SpA</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>76.452.485-3</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M185" s="2" t="n">
+        <v>2001.75</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>1495208-31-CM26</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>61.981.340-5</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>76.231.391-K</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M186" s="2" t="n">
+        <v>1652.81</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>1495208-49-CM26</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>61.981.340-5</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M187" s="2" t="n">
+        <v>879.6900000000001</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/nuble.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/nuble.xlsx
@@ -10555,7 +10555,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -10620,7 +10620,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -10685,7 +10685,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -10868,7 +10868,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -11242,7 +11242,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/nuble.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/nuble.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M187"/>
+  <dimension ref="A1:M188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4039,7 +4039,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1346280-11-CM25</t>
+          <t>1233616-7323-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.141.400-0</t>
+          <t>61.980.940-8</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>FERNANDO ALBERTO VELOSO OLIVA</t>
+          <t>KINSA SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>14.205.876-6</t>
+          <t>77.049.323-4</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4094,13 +4094,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>3184.57</v>
+        <v>788.37</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1233616-7323-CM25</t>
+          <t>1346280-11-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>69.141.400-0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>KINSA SPA</t>
+          <t>FERNANDO ALBERTO VELOSO OLIVA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>77.049.323-4</t>
+          <t>14.205.876-6</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4155,7 +4155,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>788.37</v>
+        <v>3184.57</v>
       </c>
     </row>
     <row r="61">
@@ -8934,7 +8934,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1346280-3-CM26</t>
+          <t>1346280-4-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>2072.13</v>
+        <v>3550.99</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1346280-4-CM26</t>
+          <t>1346280-3-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9039,12 +9039,12 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -9058,7 +9058,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>3550.99</v>
+        <v>2072.13</v>
       </c>
     </row>
     <row r="140">
@@ -9702,7 +9702,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2467-675-CM26</t>
+          <t>2467-674-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9742,22 +9742,26 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA DE SISTEMAS GENERADORES DE ENERGIA POWE</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>76.206.192-9</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr"/>
+          <t>76.148.628-4</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>2774.02</v>
+        <v>4194.99</v>
       </c>
     </row>
     <row r="151">
@@ -9828,7 +9832,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2467-674-CM26</t>
+          <t>2467-675-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9868,26 +9872,22 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>IMPORTADORA Y COMERCIALIZADORA DE SISTEMAS GENERADORES DE ENERGIA POWE</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.206.192-9</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>4194.99</v>
+        <v>2774.02</v>
       </c>
     </row>
     <row r="153">
@@ -10275,7 +10275,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2467-792-CM26</t>
+          <t>2467-793-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10315,17 +10315,17 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -10334,13 +10334,13 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>2139.85</v>
+        <v>4048.06</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2467-793-CM26</t>
+          <t>2467-792-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10380,17 +10380,17 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -10399,7 +10399,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>4048.06</v>
+        <v>2139.85</v>
       </c>
     </row>
     <row r="161">
@@ -10470,7 +10470,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2467-795-CM26</t>
+          <t>1375761-1284-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10490,17 +10490,17 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>61.981.330-8</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10510,17 +10510,17 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -10529,13 +10529,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>1729.9</v>
+        <v>16230.09</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1375761-1287-CM26</t>
+          <t>2467-795-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10555,17 +10555,17 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>61.981.330-8</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10575,17 +10575,17 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -10594,13 +10594,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>7687.34</v>
+        <v>1729.9</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1375761-1284-CM26</t>
+          <t>1375761-1287-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10659,7 +10659,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>16230.09</v>
+        <v>7687.34</v>
       </c>
     </row>
     <row r="165">
@@ -12107,6 +12107,67 @@
       </c>
       <c r="M187" s="2" t="n">
         <v>879.6900000000001</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>1346280-15-CM26</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>69.141.400-0</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE PRODUCTOS VIALES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>76.397.758-7</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M188" s="2" t="n">
+        <v>20129.56</v>
       </c>
     </row>
   </sheetData>
